--- a/artfynd/A 40493-2021 artfynd.xlsx
+++ b/artfynd/A 40493-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40493-2021 artfynd.xlsx
+++ b/artfynd/A 40493-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6860086</v>
+        <v>6860084</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -722,14 +717,14 @@
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr Flugebosjön Kärret öster om bäcken, Ög</t>
+          <t>Norr Flugebosjön Platån vid sandtaget, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487440.7277748829</v>
+        <v>487468</v>
       </c>
       <c r="R2" t="n">
-        <v>6440280.45996547</v>
+        <v>6440240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2013-07-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,27 +771,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per-Olof Ståhl</t>
+          <t>Per-Olof och Christina Ståhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per-Olof Ståhl</t>
+          <t>Per-Olof och Christina Ståhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6860084</v>
+        <v>6860086</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,7 +813,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -845,14 +825,14 @@
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr Flugebosjön Platån vid sandtaget, Ög</t>
+          <t>Norr Flugebosjön Kärret öster om bäcken, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487468.1309077828</v>
+        <v>487441</v>
       </c>
       <c r="R3" t="n">
-        <v>6440239.681925466</v>
+        <v>6440280</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2013-07-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,12 +879,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per-Olof Ståhl</t>
+          <t>Per-Olof och Christina Ståhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per-Olof Ståhl</t>
+          <t>Per-Olof och Christina Ståhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -924,12 +894,7 @@
         <v>6860221</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487425.3202973608</v>
+        <v>487425</v>
       </c>
       <c r="R4" t="n">
-        <v>6440263.597898419</v>
+        <v>6440264</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -997,19 +962,9 @@
           <t>2013-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per-Olof Ståhl</t>
+          <t>Per-Olof och Christina Ståhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per-Olof Ståhl</t>
+          <t>Per-Olof och Christina Ståhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 40493-2021 artfynd.xlsx
+++ b/artfynd/A 40493-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6860084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6860086</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6860221</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>